--- a/hediye listesi.xlsx
+++ b/hediye listesi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NP550P5C\Documents\Hediye_Eslestirme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188C986F-909D-4DBA-B33B-6D5E279D58DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A028B0A5-2A43-47AD-A06F-AED0FE1BDC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8100" yWindow="7110" windowWidth="15525" windowHeight="10575" xr2:uid="{0CCE99F9-BB79-4440-BF09-0608143A19B6}"/>
+    <workbookView xWindow="8100" yWindow="5025" windowWidth="15525" windowHeight="10575" xr2:uid="{0CCE99F9-BB79-4440-BF09-0608143A19B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Filtre Kahve Makinesi</t>
-  </si>
-  <si>
     <t>Bosch</t>
   </si>
   <si>
@@ -37,6 +34,9 @@
   </si>
   <si>
     <t>Kahve Cezvesi</t>
+  </si>
+  <si>
+    <t>Mutfak Robotu</t>
   </si>
 </sst>
 </file>
@@ -391,21 +391,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B63E39C-616A-4CC3-9EBF-40CE5D579A4C}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
